--- a/CRNX.xlsx
+++ b/CRNX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4460BBAF-1D0C-4509-A7B4-BA682A3F89F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50BD072-ACF7-43E7-8048-3044E45038CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4720" yWindow="5860" windowWidth="21120" windowHeight="12490" activeTab="3" xr2:uid="{EA18D026-99EE-4713-84A0-1F6E24C2FB50}"/>
+    <workbookView xWindow="11310" yWindow="3220" windowWidth="22360" windowHeight="16580" xr2:uid="{EA18D026-99EE-4713-84A0-1F6E24C2FB50}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -129,7 +129,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,6 +151,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -160,7 +167,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -168,12 +175,98 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -185,6 +278,17 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -525,30 +629,41 @@
   <cols>
     <col min="1" max="1" width="8.7265625" style="1"/>
     <col min="2" max="2" width="20" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.7265625" style="1"/>
+    <col min="3" max="3" width="10.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="16" t="s">
         <v>9</v>
       </c>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="17"/>
       <c r="K2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="1">
-        <v>32.92</v>
+      <c r="L2" s="8">
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="10" t="s">
         <v>10</v>
       </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="11"/>
       <c r="K3" s="1" t="s">
         <v>1</v>
       </c>
@@ -560,21 +675,33 @@
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B4" s="9"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="11"/>
       <c r="K4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="L4" s="2">
         <f>+L2*L3</f>
-        <v>3471.0848000000001</v>
+        <v>4428.4799999999996</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="10" t="s">
         <v>12</v>
       </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="11"/>
       <c r="K5" s="1" t="s">
         <v>3</v>
       </c>
@@ -587,9 +714,15 @@
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="9" t="s">
         <v>13</v>
       </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="11"/>
       <c r="K6" s="1" t="s">
         <v>4</v>
       </c>
@@ -601,12 +734,19 @@
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B7" s="12"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="14"/>
       <c r="K7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="L7" s="2">
         <f>+L4-L5+L6</f>
-        <v>2179.7788</v>
+        <v>3137.174</v>
       </c>
     </row>
   </sheetData>
@@ -731,7 +871,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -760,6 +900,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{E82A2F99-E270-47A9-88EF-0322312DF26E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>